--- a/branches/fix/crmi-rulesets-inheritance-safe/all-profiles.xlsx
+++ b/branches/fix/crmi-rulesets-inheritance-safe/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:27:41+00:00</t>
+    <t>2026-09-11T06:32:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/crmi-rulesets-inheritance-safe/all-profiles.xlsx
+++ b/branches/fix/crmi-rulesets-inheritance-safe/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:32:35+00:00</t>
+    <t>2026-09-11T11:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
